--- a/data/trans_orig/P78C_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P78C_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la categoría profesional que tiene o tenía en la empresa donde trabaja o trabajaba la persona sustentadora principal en 2023</t>
+          <t>Población según la categoría profesional que tiene o tenía en la empresa donde trabaja o trabajaba la persona sustentadora principal en 2023 (tasa de respuesta: 98,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>357632</t>
+          <t>358184</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>392607</t>
+          <t>395084</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>330658</t>
+          <t>332186</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>355699</t>
+          <t>356675</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>698236</t>
+          <t>699481</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>741443</t>
+          <t>744319</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,67%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10882</t>
+          <t>11016</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24392</t>
+          <t>24706</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>792</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4681</t>
+          <t>4635</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13008</t>
+          <t>12935</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27266</t>
+          <t>26739</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>550</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>8726</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10787</t>
+          <t>10503</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6295</t>
+          <t>6551</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16568</t>
+          <t>17077</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,82 +1197,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>6952</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>3765</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>11649</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>17176</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>11677</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>24245</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>1,25%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>6952</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>4022</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>11465</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>17176</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>12059</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>24694</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10221</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6018</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12864</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79096</t>
+          <t>77240</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>110618</t>
+          <t>109653</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60589</t>
+          <t>59604</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>85357</t>
+          <t>84183</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>146763</t>
+          <t>144991</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>186828</t>
+          <t>184064</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>821593</t>
+          <t>874238</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1514321</t>
+          <t>1516136</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1252218</t>
+          <t>1284468</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1556292</t>
+          <t>1557729</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2247017</t>
+          <t>2152754</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3041971</t>
+          <t>3028997</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,4%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92207</t>
+          <t>89259</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>170658</t>
+          <t>171773</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26538</t>
+          <t>25303</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53306</t>
+          <t>53033</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>138151</t>
+          <t>131447</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>215856</t>
+          <t>213276</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>866</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8265</t>
+          <t>8496</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7339</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2906</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12506</t>
+          <t>12545</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10122</t>
+          <t>9469</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>915290</t>
+          <t>853460</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11933</t>
+          <t>12732</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>15118</t>
+          <t>15366</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>929974</t>
+          <t>1061897</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56616</t>
+          <t>59474</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>108084</t>
+          <t>109607</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33016</t>
+          <t>32702</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>366729</t>
+          <t>321890</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113959</t>
+          <t>116252</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>450056</t>
+          <t>430527</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12643</t>
+          <t>13035</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33401</t>
+          <t>35329</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14252</t>
+          <t>13973</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20176</t>
+          <t>20281</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43733</t>
+          <t>43808</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2316,12 +2316,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>134788</t>
+          <t>147918</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>249559</t>
+          <t>255322</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>100724</t>
+          <t>97415</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>179478</t>
+          <t>178634</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>276053</t>
+          <t>274064</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>415801</t>
+          <t>419934</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>355493</t>
+          <t>355350</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>404543</t>
+          <t>403876</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>439256</t>
+          <t>437674</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>474014</t>
+          <t>473121</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>805844</t>
+          <t>806478</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>867887</t>
+          <t>870448</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,96%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>70875</t>
+          <t>71170</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>107170</t>
+          <t>105874</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>42106</t>
+          <t>41956</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64796</t>
+          <t>64127</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>119020</t>
+          <t>120762</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>160487</t>
+          <t>162320</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6727</t>
+          <t>6784</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19783</t>
+          <t>20429</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>161</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>5979</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21799</t>
+          <t>22837</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9870</t>
+          <t>9466</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>28702</t>
+          <t>28335</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4519</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>13677</t>
+          <t>14150</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>15797</t>
+          <t>16222</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>35974</t>
+          <t>38321</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13363</t>
+          <t>13945</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12263</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26881</t>
+          <t>26923</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>30135</t>
+          <t>29463</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>52483</t>
+          <t>50428</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -3111,12 +3111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7126</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20515</t>
+          <t>20809</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3126,12 +3126,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>8943</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>25552</t>
+          <t>25785</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -3224,12 +3224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>57172</t>
+          <t>57845</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>89682</t>
+          <t>91520</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>52308</t>
+          <t>53416</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>78688</t>
+          <t>79166</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>119374</t>
+          <t>119040</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>159821</t>
+          <t>160089</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1589067</t>
+          <t>1599674</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2271027</t>
+          <t>2272462</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2080174</t>
+          <t>2080640</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2364936</t>
+          <t>2367330</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3614676</t>
+          <t>3661390</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4584165</t>
+          <t>4589141</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>77,01%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>185518</t>
+          <t>188631</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>279234</t>
+          <t>284222</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>73538</t>
+          <t>74265</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>114724</t>
+          <t>114273</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>283602</t>
+          <t>286932</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>380304</t>
+          <t>380157</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8622</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>24973</t>
+          <t>24939</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11357</t>
+          <t>10801</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>13999</t>
+          <t>14147</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>31535</t>
+          <t>32168</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -3793,12 +3793,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>27706</t>
+          <t>27603</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>940061</t>
+          <t>959064</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10946</t>
+          <t>10896</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>26292</t>
+          <t>25994</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>43864</t>
+          <t>42448</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1256336</t>
+          <t>1173344</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>89095</t>
+          <t>87122</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>140817</t>
+          <t>138117</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>57799</t>
+          <t>56806</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>395008</t>
+          <t>383319</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>171567</t>
+          <t>166803</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>497816</t>
+          <t>542267</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -4019,12 +4019,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>27513</t>
+          <t>27625</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>54863</t>
+          <t>55105</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>8442</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>21375</t>
+          <t>22201</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>40509</t>
+          <t>40533</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>70721</t>
+          <t>69945</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -4132,12 +4132,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>290270</t>
+          <t>287026</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>423937</t>
+          <t>425756</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>224036</t>
+          <t>211629</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>321860</t>
+          <t>321286</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>563722</t>
+          <t>564319</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>736104</t>
+          <t>731298</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P78C_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P78C_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>376808</t>
+          <t>428100</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>358184</t>
+          <t>406881</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>395084</t>
+          <t>445902</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>344295</t>
+          <t>378107</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>332186</t>
+          <t>364412</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>356675</t>
+          <t>391286</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>721103</t>
+          <t>806207</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>699481</t>
+          <t>779995</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>744319</t>
+          <t>828699</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,94%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16744</t>
+          <t>18124</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11016</t>
+          <t>12204</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24706</t>
+          <t>26977</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,22 +873,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>2251</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>857</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4635</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>18873</t>
+          <t>20376</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12935</t>
+          <t>13010</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26739</t>
+          <t>28960</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>763</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>431</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>562</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2184</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8726</t>
+          <t>9052</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4509</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>1687</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10503</t>
+          <t>13314</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10223</t>
+          <t>10888</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6551</t>
+          <t>6355</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17077</t>
+          <t>18300</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7414</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3765</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11649</t>
+          <t>12744</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>17176</t>
+          <t>18302</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11677</t>
+          <t>12238</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24245</t>
+          <t>26034</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -1290,22 +1290,22 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5214</t>
+          <t>5524</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>2443</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11715</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>6892</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>14009</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -1403,32 +1403,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>92975</t>
+          <t>102675</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77240</t>
+          <t>86154</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>109653</t>
+          <t>121032</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1438,32 +1438,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>71594</t>
+          <t>75800</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59604</t>
+          <t>63726</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84183</t>
+          <t>87820</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,32 +1473,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>164569</t>
+          <t>178475</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>144991</t>
+          <t>158997</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>184064</t>
+          <t>201779</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -1516,17 +1516,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>505056</t>
+          <t>568589</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>505056</t>
+          <t>568589</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>505056</t>
+          <t>568589</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1551,17 +1551,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>429237</t>
+          <t>468080</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>429237</t>
+          <t>468080</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>429237</t>
+          <t>468080</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1586,17 +1586,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>934293</t>
+          <t>1036669</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>934293</t>
+          <t>1036669</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>934293</t>
+          <t>1036669</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1324688</t>
+          <t>1468354</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>874238</t>
+          <t>1428026</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1516136</t>
+          <t>1511468</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1464723</t>
+          <t>1371184</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1284468</t>
+          <t>1343919</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1557729</t>
+          <t>1395262</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2789412</t>
+          <t>2839538</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2152754</t>
+          <t>2787039</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3028997</t>
+          <t>2888637</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,48%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>138694</t>
+          <t>152389</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89259</t>
+          <t>130041</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>171773</t>
+          <t>176212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>40723</t>
+          <t>45825</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25303</t>
+          <t>34864</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53033</t>
+          <t>58496</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>179418</t>
+          <t>198213</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131447</t>
+          <t>170963</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>213276</t>
+          <t>230640</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
+          <t>5,45%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>4,7%</t>
         </is>
       </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>10428</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>9486</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>4037</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12545</t>
+          <t>13892</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>254669</t>
+          <t>12756</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9469</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>853460</t>
+          <t>20361</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>8286</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12732</t>
+          <t>14295</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>261573</t>
+          <t>21042</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>15366</t>
+          <t>13549</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1061897</t>
+          <t>30456</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>85527</t>
+          <t>90624</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>59474</t>
+          <t>73243</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>109607</t>
+          <t>110735</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>105839</t>
+          <t>41778</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32702</t>
+          <t>31783</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>321890</t>
+          <t>53352</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>191365</t>
+          <t>132401</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>116252</t>
+          <t>112231</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>430527</t>
+          <t>154867</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -2198,32 +2198,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22234</t>
+          <t>28383</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13035</t>
+          <t>18624</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35329</t>
+          <t>42231</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,32 +2233,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7993</t>
+          <t>10222</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13973</t>
+          <t>16515</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>30227</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20281</t>
+          <t>27571</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43808</t>
+          <t>54255</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -2311,32 +2311,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>209799</t>
+          <t>228924</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>147918</t>
+          <t>199659</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>255322</t>
+          <t>262926</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2346,32 +2346,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>146596</t>
+          <t>167835</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>97415</t>
+          <t>146862</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>178634</t>
+          <t>190010</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2381,32 +2381,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>356395</t>
+          <t>396759</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>274064</t>
+          <t>359573</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>419934</t>
+          <t>436679</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -2424,17 +2424,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2038676</t>
+          <t>1984954</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2038676</t>
+          <t>1984954</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2038676</t>
+          <t>1984954</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2459,17 +2459,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1776409</t>
+          <t>1649693</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1776409</t>
+          <t>1649693</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1776409</t>
+          <t>1649693</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2494,17 +2494,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3815085</t>
+          <t>3634647</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3815085</t>
+          <t>3634647</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3815085</t>
+          <t>3634647</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>379952</t>
+          <t>409869</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>355350</t>
+          <t>384828</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>403876</t>
+          <t>436524</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>456560</t>
+          <t>500443</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>437674</t>
+          <t>481209</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>473121</t>
+          <t>518907</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>836512</t>
+          <t>910311</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>806478</t>
+          <t>876099</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>870448</t>
+          <t>941840</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>70,41%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>87576</t>
+          <t>98091</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>71170</t>
+          <t>81315</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>105874</t>
+          <t>117697</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>52835</t>
+          <t>61252</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>41956</t>
+          <t>50551</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64127</t>
+          <t>76497</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>140411</t>
+          <t>159343</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>120762</t>
+          <t>138509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>162320</t>
+          <t>182842</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>11997</t>
+          <t>12483</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6784</t>
+          <t>7398</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20429</t>
+          <t>21187</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>659</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>7086</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>13883</t>
+          <t>14909</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>8576</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22837</t>
+          <t>23700</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>16187</t>
+          <t>18468</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>28335</t>
+          <t>32617</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4519</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14150</t>
+          <t>16513</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>24359</t>
+          <t>28365</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16222</t>
+          <t>19013</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>38321</t>
+          <t>42599</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -2993,32 +2993,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>21074</t>
+          <t>24455</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13945</t>
+          <t>16062</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30317</t>
+          <t>34380</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3028,32 +3028,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>18156</t>
+          <t>19797</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12497</t>
+          <t>13501</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26923</t>
+          <t>29476</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3063,32 +3063,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>39230</t>
+          <t>44253</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>29463</t>
+          <t>33347</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>50428</t>
+          <t>56653</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -3106,32 +3106,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>12501</t>
+          <t>13983</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20809</t>
+          <t>23897</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3141,32 +3141,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1803</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8943</t>
+          <t>9568</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3176,22 +3176,22 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>17071</t>
+          <t>18756</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>11879</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>25785</t>
+          <t>28213</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -3219,32 +3219,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>72565</t>
+          <t>85459</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>57845</t>
+          <t>68757</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>91520</t>
+          <t>102400</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3254,32 +3254,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>65568</t>
+          <t>76204</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>53416</t>
+          <t>62492</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>79166</t>
+          <t>91068</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3289,32 +3289,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>138133</t>
+          <t>161663</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>119040</t>
+          <t>138597</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>160089</t>
+          <t>184526</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -3332,17 +3332,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>601852</t>
+          <t>662809</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>601852</t>
+          <t>662809</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>601852</t>
+          <t>662809</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3367,17 +3367,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>607747</t>
+          <t>674792</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>607747</t>
+          <t>674792</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>607747</t>
+          <t>674792</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3402,17 +3402,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1209599</t>
+          <t>1337600</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1209599</t>
+          <t>1337600</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1209599</t>
+          <t>1337600</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2081448</t>
+          <t>2306323</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1599674</t>
+          <t>2253545</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2272462</t>
+          <t>2357053</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2265578</t>
+          <t>2249734</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2080640</t>
+          <t>2209445</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2367330</t>
+          <t>2279045</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>4347027</t>
+          <t>4556058</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3661390</t>
+          <t>4490928</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4589141</t>
+          <t>4616354</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>76,83%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>243015</t>
+          <t>268604</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>188631</t>
+          <t>235157</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>284222</t>
+          <t>300611</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>95687</t>
+          <t>109329</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>74265</t>
+          <t>94273</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>114273</t>
+          <t>128227</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>338702</t>
+          <t>377932</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>286932</t>
+          <t>343673</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>380157</t>
+          <t>413661</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>15827</t>
+          <t>16769</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>10459</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>24939</t>
+          <t>27860</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>21749</t>
+          <t>24190</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14147</t>
+          <t>16128</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>32168</t>
+          <t>36391</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -3788,32 +3788,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>273182</t>
+          <t>33740</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>27603</t>
+          <t>23100</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>959064</t>
+          <t>48953</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3823,32 +3823,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>17259</t>
+          <t>20503</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10896</t>
+          <t>14204</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>25994</t>
+          <t>29290</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3858,32 +3858,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>290441</t>
+          <t>54243</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>42448</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1173344</t>
+          <t>72618</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -3901,32 +3901,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>116824</t>
+          <t>125967</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>87122</t>
+          <t>105798</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>138117</t>
+          <t>148353</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3936,32 +3936,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>130947</t>
+          <t>68989</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>56806</t>
+          <t>57439</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>383319</t>
+          <t>85144</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3971,32 +3971,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>247772</t>
+          <t>194956</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>166803</t>
+          <t>171663</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>542267</t>
+          <t>222476</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -4014,32 +4014,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>39949</t>
+          <t>47891</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>27625</t>
+          <t>36174</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>55105</t>
+          <t>64857</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4049,32 +4049,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>14241</t>
+          <t>16750</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>8999</t>
+          <t>10780</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>22201</t>
+          <t>24883</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4084,32 +4084,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>54190</t>
+          <t>64641</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>40533</t>
+          <t>50832</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>69945</t>
+          <t>82900</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -4127,32 +4127,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>375339</t>
+          <t>417058</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>287026</t>
+          <t>376896</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>425756</t>
+          <t>453964</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4162,32 +4162,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>283759</t>
+          <t>319839</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>211629</t>
+          <t>291691</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>321286</t>
+          <t>348685</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4197,32 +4197,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>659097</t>
+          <t>736898</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>564319</t>
+          <t>692468</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>731298</t>
+          <t>785784</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -4240,17 +4240,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3145584</t>
+          <t>3216352</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3145584</t>
+          <t>3216352</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3145584</t>
+          <t>3216352</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2813393</t>
+          <t>2792564</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2813393</t>
+          <t>2792564</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2813393</t>
+          <t>2792564</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,17 +4310,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>5958977</t>
+          <t>6008917</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5958977</t>
+          <t>6008917</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5958977</t>
+          <t>6008917</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
